--- a/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
+++ b/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4E6F55-B98C-4928-9C66-5510BF8B9FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD69AB4-AECB-4EF4-8FCC-756FC02B3398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14655" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <t>kspero@hl.com.test</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -686,7 +686,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -724,7 +724,7 @@
     <hyperlink ref="A3" r:id="rId1" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{F5167E44-EE84-48EC-B6E8-69243B861AB5}"/>
     <hyperlink ref="A2" r:id="rId2" tooltip="mailto:kspero@hl.com.test" display="mailto:kspero@hl.com.test" xr:uid="{D9C78D91-C519-47A3-80B2-C808030C1CD6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{873F882F-38ED-48DD-8BEC-C4D6749440FB}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{2D0A72A9-1B1C-4CD5-944C-33006FE81F8C}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{DA4B1409-C834-4740-83F6-9F9713F7B0F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
+++ b/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD69AB4-AECB-4EF4-8FCC-756FC02B3398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A952D3-8743-4FA5-8ECE-8C31BAACB575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
-    <sheet name="Approver" sheetId="3" r:id="rId2"/>
-    <sheet name="Users" sheetId="2" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="4" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="5" r:id="rId3"/>
+    <sheet name="ExpenseRequest" sheetId="1" r:id="rId4"/>
+    <sheet name="Approver" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>LOB</t>
   </si>
@@ -150,6 +152,18 @@
   </si>
   <si>
     <t>Bingo@12345</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Expense Request(LWC)</t>
   </si>
 </sst>
 </file>
@@ -487,190 +501,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3">
+      <c r="B3">
         <v>4</v>
       </c>
     </row>
@@ -681,15 +538,252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E224C-9705-4F3F-99CA-4DF15C406A73}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047AFE0-B79F-4D30-A72F-B1E8729D8B25}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -697,7 +791,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -708,7 +802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -728,41 +822,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
+++ b/TestData/TMTI0075756_75765_EventExpense_EmailNotification_RequestMoreInformationApproveAsFirstLevelApprover.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4E6F55-B98C-4928-9C66-5510BF8B9FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A952D3-8743-4FA5-8ECE-8C31BAACB575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14655" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
-    <sheet name="Approver" sheetId="3" r:id="rId2"/>
-    <sheet name="Users" sheetId="2" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="4" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="5" r:id="rId3"/>
+    <sheet name="ExpenseRequest" sheetId="1" r:id="rId4"/>
+    <sheet name="Approver" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>LOB</t>
   </si>
@@ -149,7 +151,19 @@
     <t>kspero@hl.com.test</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Expense Request(LWC)</t>
   </si>
 </sst>
 </file>
@@ -487,190 +501,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3">
+      <c r="B3">
         <v>4</v>
       </c>
     </row>
@@ -681,15 +538,252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E224C-9705-4F3F-99CA-4DF15C406A73}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047AFE0-B79F-4D30-A72F-B1E8729D8B25}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -697,7 +791,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -708,7 +802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -724,45 +818,8 @@
     <hyperlink ref="A3" r:id="rId1" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{F5167E44-EE84-48EC-B6E8-69243B861AB5}"/>
     <hyperlink ref="A2" r:id="rId2" tooltip="mailto:kspero@hl.com.test" display="mailto:kspero@hl.com.test" xr:uid="{D9C78D91-C519-47A3-80B2-C808030C1CD6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{873F882F-38ED-48DD-8BEC-C4D6749440FB}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{2D0A72A9-1B1C-4CD5-944C-33006FE81F8C}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{DA4B1409-C834-4740-83F6-9F9713F7B0F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>